--- a/dataset_t6_grouped/results2/G4/G4_T8482_W0038F0001T0006Z000C1N25_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T8482_W0038F0001T0006Z000C1N25_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>53.00890136422765</v>
+        <v>8.613946471686994</v>
       </c>
       <c r="D2" t="n">
-        <v>48.00497845945588</v>
+        <v>7.80080899966158</v>
       </c>
       <c r="E2" t="n">
-        <v>14.1495790604457</v>
+        <v>2.299306597322427</v>
       </c>
       <c r="F2" t="n">
-        <v>12.7055838525485</v>
+        <v>2.064657376039132</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>59.42244278679706</v>
+        <v>9.656146952854524</v>
       </c>
       <c r="D3" t="n">
-        <v>27.14030997615489</v>
+        <v>4.410300371125169</v>
       </c>
       <c r="E3" t="n">
-        <v>14.1495790604457</v>
+        <v>2.299306597322427</v>
       </c>
       <c r="F3" t="n">
-        <v>12.7055838525485</v>
+        <v>2.064657376039132</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>43.27195558083687</v>
+        <v>7.031692781885991</v>
       </c>
       <c r="D4" t="n">
-        <v>38.20571520045331</v>
+        <v>6.208428720073663</v>
       </c>
       <c r="E4" t="n">
-        <v>14.1495790604457</v>
+        <v>2.299306597322427</v>
       </c>
       <c r="F4" t="n">
-        <v>12.7055838525485</v>
+        <v>2.064657376039132</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>60.26436586591608</v>
+        <v>9.792959453211363</v>
       </c>
       <c r="D5" t="n">
-        <v>6.49236547013746</v>
+        <v>1.055009388897337</v>
       </c>
       <c r="E5" t="n">
-        <v>14.1495790604457</v>
+        <v>2.299306597322427</v>
       </c>
       <c r="F5" t="n">
-        <v>12.7055838525485</v>
+        <v>2.064657376039132</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>26.91904451282632</v>
+        <v>4.374344733334278</v>
       </c>
       <c r="D6" t="n">
-        <v>22.6220946562851</v>
+        <v>3.676090381646329</v>
       </c>
       <c r="E6" t="n">
-        <v>14.1495790604457</v>
+        <v>2.299306597322427</v>
       </c>
       <c r="F6" t="n">
-        <v>12.7055838525485</v>
+        <v>2.064657376039132</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>71.282387083673</v>
+        <v>11.58338790109686</v>
       </c>
       <c r="D7" t="n">
-        <v>28.93181278174027</v>
+        <v>4.701419577032794</v>
       </c>
       <c r="E7" t="n">
-        <v>14.1495790604457</v>
+        <v>2.299306597322427</v>
       </c>
       <c r="F7" t="n">
-        <v>12.7055838525485</v>
+        <v>2.064657376039132</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>67.76180863833672</v>
+        <v>11.01129390372972</v>
       </c>
       <c r="D8" t="n">
-        <v>18.45104888560767</v>
+        <v>2.998295443911246</v>
       </c>
       <c r="E8" t="n">
-        <v>14.1495790604457</v>
+        <v>2.299306597322427</v>
       </c>
       <c r="F8" t="n">
-        <v>12.7055838525485</v>
+        <v>2.064657376039132</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>24.01207453954104</v>
+        <v>3.90196211267542</v>
       </c>
       <c r="D9" t="n">
-        <v>28.83008635396624</v>
+        <v>4.684889032519513</v>
       </c>
       <c r="E9" t="n">
-        <v>14.1495790604457</v>
+        <v>2.299306597322427</v>
       </c>
       <c r="F9" t="n">
-        <v>12.7055838525485</v>
+        <v>2.064657376039132</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>33.10252506121091</v>
+        <v>5.379160322446773</v>
       </c>
       <c r="D10" t="n">
-        <v>38.17894798711986</v>
+        <v>6.204079047906976</v>
       </c>
       <c r="E10" t="n">
-        <v>14.1495790604457</v>
+        <v>2.299306597322427</v>
       </c>
       <c r="F10" t="n">
-        <v>12.7055838525485</v>
+        <v>2.064657376039132</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>47.35957717940097</v>
+        <v>7.695931291652657</v>
       </c>
       <c r="D11" t="n">
-        <v>22.30665512423027</v>
+        <v>3.624831457687419</v>
       </c>
       <c r="E11" t="n">
-        <v>14.1495790604457</v>
+        <v>2.299306597322427</v>
       </c>
       <c r="F11" t="n">
-        <v>12.7055838525485</v>
+        <v>2.064657376039132</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>47.92421895219064</v>
+        <v>7.787685579730979</v>
       </c>
       <c r="D12" t="n">
-        <v>47.57921935120408</v>
+        <v>7.731623144570664</v>
       </c>
       <c r="E12" t="n">
-        <v>14.1495790604457</v>
+        <v>2.299306597322427</v>
       </c>
       <c r="F12" t="n">
-        <v>12.7055838525485</v>
+        <v>2.064657376039132</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>55.92096722911491</v>
+        <v>9.087157174731173</v>
       </c>
       <c r="D13" t="n">
-        <v>36.80089090186557</v>
+        <v>5.980144771553156</v>
       </c>
       <c r="E13" t="n">
-        <v>14.1495790604457</v>
+        <v>2.299306597322427</v>
       </c>
       <c r="F13" t="n">
-        <v>12.7055838525485</v>
+        <v>2.064657376039132</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>63.6009436546116</v>
+        <v>10.33515334387439</v>
       </c>
       <c r="D14" t="n">
-        <v>18.70608908832139</v>
+        <v>3.039739476852226</v>
       </c>
       <c r="E14" t="n">
-        <v>14.1495790604457</v>
+        <v>2.299306597322427</v>
       </c>
       <c r="F14" t="n">
-        <v>12.7055838525485</v>
+        <v>2.064657376039132</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>42.32447249194185</v>
+        <v>6.877726779940551</v>
       </c>
       <c r="D15" t="n">
-        <v>42.02791310528347</v>
+        <v>6.829535879608565</v>
       </c>
       <c r="E15" t="n">
-        <v>14.1495790604457</v>
+        <v>2.299306597322427</v>
       </c>
       <c r="F15" t="n">
-        <v>12.7055838525485</v>
+        <v>2.064657376039132</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>58.61783162361184</v>
+        <v>9.525397638836925</v>
       </c>
       <c r="D16" t="n">
-        <v>56.53730018907459</v>
+        <v>9.187311280724622</v>
       </c>
       <c r="E16" t="n">
-        <v>14.1495790604457</v>
+        <v>2.299306597322427</v>
       </c>
       <c r="F16" t="n">
-        <v>12.7055838525485</v>
+        <v>2.064657376039132</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>69.07802696504648</v>
+        <v>11.22517938182005</v>
       </c>
       <c r="D17" t="n">
-        <v>25.06641945455068</v>
+        <v>4.073293161364486</v>
       </c>
       <c r="E17" t="n">
-        <v>14.1495790604457</v>
+        <v>2.299306597322427</v>
       </c>
       <c r="F17" t="n">
-        <v>12.7055838525485</v>
+        <v>2.064657376039132</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
